--- a/output/2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx
+++ b/output/2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -573,8 +573,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Azienda reale verificata: distributore/importatore ufficiale Nilfisk per Croazia (e Bosnia-Erzegovina) dal 2013, con catalogo di attrezzature per pulizia professionale (aspiratori, lavasciuga, estrattori) confermato sul sito crom.hr. Nessuna sede fisica confermata in Zadarska županija: copertura a livello nazionale che include potenzialmente il territorio di Zadar, ma senza filiale locale accertata. Telefono ed email non reperiti da fonti verificabili, non inventati.</t>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -607,8 +605,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Azienda reale verificata tramite sito dalbo.hr: vendita, noleggio e assistenza macchine per lavaggio/pulizia/spazzamento pavimenti (RCM, TSM, Comac, Biemmedue, Kärcher, Nilfisk, Taski, Hako e altri marchi). Sede legale a Varaždin (Braće Vidović 18); nessuna sede fisica confermata in Zadarska županija, copertura nazionale. Telefono ed email non reperiti da fonti verificabili.</t>
@@ -616,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -646,7 +642,6 @@
           <t>+385 43 221 455</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Azienda reale verificata tramite annavi.hr e nkim.hr: produttore/distributore del marchio croato Annavi (in collaborazione con il produttore italiano IPC-group) e rivenditore Kärcher, con macchine per lavaggio/pulizia pavimenti, spazzatrici, aspiratori, idropulitrici. Sede a Pupelica 64, Šandrovac (Bjelovar), Bjelovarsko-bilogorska županija; nessuna sede fisica confermata in Zadarska županija, prodotti reperibili verosimilmente solo tramite vendita a distanza/rivenditori. Telefono riportato è quello della sede di Bjelovar/Šandrovac, non una linea dedicata a Zadar. Email non reperita da fonti verificabili.</t>
@@ -654,7 +649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx
+++ b/output/2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Azienda reale verificata: distributore/importatore ufficiale Nilfisk per Croazia (e Bosnia-Erzegovina) dal 2013, con catalogo di attrezzature per pulizia professionale (aspiratori, lavasciuga, estrattori) confermato sul sito crom.hr. Nessuna sede fisica confermata in Zadarska županija: copertura a livello nazionale che include potenzialmente il territorio di Zadar, ma senza filiale locale accertata. Telefono ed email non reperiti da fonti verificabili, non inventati.</t>
+          <t>Azienda reale verificata: distributore/importatore ufficiale Nilfisk per Croazia (e Bosnia-Erzegovina) dal 2013, con catalogo di attrezzature per pulizia professionale (aspiratori, lavasciuga, estrattori) confermato sul sito crom.hr. Nessuna sede fisica confermata in Zadarska županija: copertura a livello nazionale che include potenzialmente il territorio di Zadar, ma senza filiale locale accertata. Telefono ed email non reperiti da fonti verificabili, non inventati. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Azienda reale verificata tramite sito dalbo.hr: vendita, noleggio e assistenza macchine per lavaggio/pulizia/spazzamento pavimenti (RCM, TSM, Comac, Biemmedue, Kärcher, Nilfisk, Taski, Hako e altri marchi). Sede legale a Varaždin (Braće Vidović 18); nessuna sede fisica confermata in Zadarska županija, copertura nazionale. Telefono ed email non reperiti da fonti verificabili.</t>
+          <t>Azienda reale verificata tramite sito dalbo.hr: vendita, noleggio e assistenza macchine per lavaggio/pulizia/spazzamento pavimenti (RCM, TSM, Comac, Biemmedue, Kärcher, Nilfisk, Taski, Hako e altri marchi). Sede legale a Varaždin (Braće Vidović 18); nessuna sede fisica confermata in Zadarska županija, copertura nazionale. Telefono ed email non reperiti da fonti verificabili. [DUPLICATO — vedi anche: 2026-09-12_22_Croazia_Varazdinska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/output/2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx
+++ b/output/2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Filiale di Zadar (Zagrebačka 47, zona 'dvi pumpe') aperta nel 2023, confermata da karcher.com (Kärcher Center Servis Brišart), antenazadar.hr e 057info.hr. Sede legale a Sesvete/Zagabria. Vendita e assistenza macchine per pulizia industriale/professionale a marchio Kärcher e detergenti professionali. Email info@brisart.eu è quella aziendale generale; servis-zadar@karcher.com è il contatto specifico del servizio Zadar riportato da karcher.com.</t>
+          <t>Filiale di Zadar (Zagrebačka 47, zona 'dvi pumpe') aperta nel 2023, confermata da karcher.com (Kärcher Center Servis Brišart), antenazadar.hr e 057info.hr. Sede legale a Sesvete/Zagabria. Vendita e assistenza macchine per pulizia industriale/professionale a marchio Kärcher e detergenti professionali. Email info@brisart.eu è quella aziendale generale; servis-zadar@karcher.com è il contatto specifico del servizio Zadar riportato da karcher.com. [DUPLICATO — vedi anche: 2026-09-14_20_Croazia_Virovitico-podravska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
